--- a/Excel/24-div-26q1.xlsx
+++ b/Excel/24-div-26q1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_085DDD1F504120DEE54878D642782EBDB11F8448" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E17FFF-1E76-4B26-A900-404D37545920}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_085DDD1F504120DEE54878D642782EBDB11F8448" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF0647A-7E71-4343-B014-FD95484D3363}"/>
   <bookViews>
-    <workbookView xWindow="12192" yWindow="876" windowWidth="10608" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10848" yWindow="1008" windowWidth="11256" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="paiddate" sheetId="2" r:id="rId1"/>
+    <sheet name="xdate" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>name</t>
   </si>
@@ -108,6 +109,12 @@
   </si>
   <si>
     <t>AIMIRT</t>
+  </si>
+  <si>
+    <t>MAM</t>
+  </si>
+  <si>
+    <t>3BBIF</t>
   </si>
 </sst>
 </file>
@@ -115,16 +122,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="187" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="188" formatCode="0.0000"/>
-    <numFmt numFmtId="189" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="[$฿-41E]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,14 +144,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,30 +199,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,19 +530,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9EDF94E-FDC8-4460-BB4E-44FB436D24A2}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.796875" style="5"/>
-    <col min="3" max="3" width="8.796875" style="7"/>
-    <col min="4" max="4" width="9.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="8.88671875" style="7"/>
+    <col min="4" max="4" width="9.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +568,433 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.1915</v>
+      </c>
+      <c r="C2" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="9">
+        <v>3830</v>
+      </c>
+      <c r="E2" s="13">
+        <v>3447</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3">
+        <v>46161</v>
+      </c>
+      <c r="H2" s="3">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="C3" s="7">
+        <v>900</v>
+      </c>
+      <c r="D3" s="9">
+        <f>B3*C3</f>
+        <v>184.5</v>
+      </c>
+      <c r="E3" s="13">
+        <f>D3*0.9</f>
+        <v>166.05</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46164</v>
+      </c>
+      <c r="G3" s="3">
+        <v>46164</v>
+      </c>
+      <c r="H3" s="3">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45000</v>
+      </c>
+      <c r="D4" s="9">
+        <v>9999</v>
+      </c>
+      <c r="E4" s="13">
+        <v>8999.1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3">
+        <v>46157</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="12">
+        <v>0.1946</v>
+      </c>
+      <c r="C5" s="7">
+        <v>69000</v>
+      </c>
+      <c r="D5" s="9">
+        <v>13427.4</v>
+      </c>
+      <c r="E5" s="13">
+        <v>12084.66</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3">
+        <v>46168</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C6" s="7">
+        <v>55000</v>
+      </c>
+      <c r="D6" s="9">
+        <v>15400</v>
+      </c>
+      <c r="E6" s="13">
+        <v>13860</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3">
+        <v>46170</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C7" s="7">
+        <v>7200</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1260</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1134</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3">
+        <v>46170</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="C8" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D8" s="9">
+        <v>3010</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2709</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3">
+        <v>46169</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.1434</v>
+      </c>
+      <c r="C9" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="9">
+        <f>B9*C9</f>
+        <v>7170</v>
+      </c>
+      <c r="E9" s="13">
+        <f>D9*0.9</f>
+        <v>6453</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46164</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E10" s="13">
+        <f>SUM(E2:E9)</f>
+        <v>48852.81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C11" s="7">
+        <v>55000</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" ref="D11:D16" si="0">B11*C11</f>
+        <v>15400.000000000002</v>
+      </c>
+      <c r="E11" s="14">
+        <f>D11*0.9</f>
+        <v>13860.000000000002</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3">
+        <v>46170</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C12" s="7">
+        <v>24000</v>
+      </c>
+      <c r="D12" s="10">
+        <f t="shared" si="0"/>
+        <v>6720.0000000000009</v>
+      </c>
+      <c r="E12" s="14">
+        <f>D12*0.9</f>
+        <v>6048.0000000000009</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="3">
+        <v>46170</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C13" s="7">
+        <f>SUM(C11:C12)</f>
+        <v>79000</v>
+      </c>
+      <c r="D13" s="9">
+        <f t="shared" si="0"/>
+        <v>22120.000000000004</v>
+      </c>
+      <c r="E13" s="14">
+        <f>E11+E12</f>
+        <v>19908.000000000004</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3">
+        <v>46170</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C14" s="7">
+        <v>120000</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="0"/>
+        <v>16800</v>
+      </c>
+      <c r="E14" s="10">
+        <f>D14</f>
+        <v>16800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C15" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+      <c r="E15" s="10">
+        <f>D15</f>
+        <v>4200</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C14:C15)</f>
+        <v>150000</v>
+      </c>
+      <c r="D16" s="9">
+        <f t="shared" si="0"/>
+        <v>42000.000000000007</v>
+      </c>
+      <c r="E16" s="14">
+        <f>E14+E15</f>
+        <v>21000</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46177</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H9">
+    <sortCondition ref="H2:H9"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.77734375" style="5"/>
+    <col min="3" max="3" width="8.77734375" style="7"/>
+    <col min="4" max="4" width="9.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -577,7 +1020,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -590,7 +1033,7 @@
       <c r="D3" s="9">
         <v>3830</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="13">
         <v>3447</v>
       </c>
       <c r="F3" t="s">
@@ -603,7 +1046,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -631,7 +1074,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -657,7 +1100,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -683,7 +1126,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -709,7 +1152,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -735,7 +1178,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -763,13 +1206,13 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E10" s="9">
         <f>SUM(E2:E9)</f>
         <v>48852.81</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -797,7 +1240,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -825,7 +1268,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -852,6 +1295,82 @@
       </c>
       <c r="H13" s="3">
         <v>46184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C14" s="7">
+        <v>120000</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" ref="D14:D16" si="1">B14*C14</f>
+        <v>16800</v>
+      </c>
+      <c r="E14" s="10">
+        <f>D14</f>
+        <v>16800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C15" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+      <c r="E15" s="10">
+        <f>D15</f>
+        <v>4200</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C14:C15)</f>
+        <v>150000</v>
+      </c>
+      <c r="D16" s="9">
+        <f t="shared" si="1"/>
+        <v>42000.000000000007</v>
+      </c>
+      <c r="E16" s="10">
+        <f>E14+E15</f>
+        <v>21000</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46177</v>
       </c>
     </row>
   </sheetData>
